--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/los-rios.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M182"/>
+  <dimension ref="A1:M183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1718.43</v>
+        <v>1709.6</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2025.89</v>
+        <v>2005.68</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>7042.54</v>
+        <v>6964.07</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1133.15</v>
+        <v>1145.48</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1723.51</v>
+        <v>1735.45</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1977.25</v>
+        <v>1986.46</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1154.14</v>
+        <v>1162.46</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4269.97</v>
+        <v>4300.75</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>4693.12</v>
+        <v>4717.35</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1255.47</v>
+        <v>1239.53</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2188.24</v>
+        <v>2183.5</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1695.84</v>
+        <v>1688.73</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>917.2</v>
+        <v>906.59</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>760.5</v>
+        <v>754.05</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1102.67</v>
+        <v>1106.9</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1721.56</v>
+        <v>1729.36</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1925.1</v>
+        <v>1930.2</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1985.73</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4279.46</v>
+        <v>4308.91</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>786.9</v>
+        <v>795.34</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>6168.36</v>
+        <v>6244.17</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1091.45</v>
+        <v>1097.42</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1286.1</v>
+        <v>1267.66</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1311.34</v>
+        <v>1292.44</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2067.77</v>
+        <v>2041.05</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1711.56</v>
+        <v>1711.57</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1233.8</v>
+        <v>1232.96</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1828.22</v>
+        <v>1821.94</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1313.75</v>
+        <v>1309.24</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2314.13</v>
+        <v>2306.19</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1490.94</v>
+        <v>1483.06</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1719.76</v>
+        <v>1710.67</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3207.75</v>
+        <v>3187.64</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1589.92</v>
+        <v>1600.34</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>951.28</v>
+        <v>964.09</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>11476.45</v>
+        <v>11651.17</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3166.29</v>
+        <v>3262.3</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>4862.48</v>
+        <v>4826.09</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1031.91</v>
+        <v>1034.9</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1572.02</v>
+        <v>1576.58</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1771.34</v>
+        <v>1776.48</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1241.81</v>
+        <v>1245.41</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>10822.94</v>
+        <v>10878.84</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1952.89</v>
+        <v>1958.25</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1708.95</v>
+        <v>1724.5</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2105.92</v>
+        <v>2125.07</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>818.5</v>
+        <v>825.9400000000001</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2206.91</v>
+        <v>2226.98</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3749.1</v>
+        <v>3775.21</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1919.42</v>
+        <v>1932.06</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1242.94</v>
+        <v>1254.01</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>5398.95</v>
+        <v>5447.03</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1232.08</v>
+        <v>1243.05</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>938.73</v>
+        <v>947.09</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1336.99</v>
+        <v>1348.9</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2368.21</v>
+        <v>2364.15</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1991.75</v>
+        <v>1988.34</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>8494.940000000001</v>
+        <v>8482.440000000001</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>2120</v>
+        <v>2108.46</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>912.36</v>
+        <v>907.39</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3996.1</v>
+        <v>3972.55</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>856.4400000000001</v>
+        <v>851.39</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2002.01</v>
+        <v>1989.84</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>811.41</v>
+        <v>806.48</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>6889.14</v>
+        <v>6862.55</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>6455.41</v>
+        <v>6488.83</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>7239.75</v>
+        <v>7450.04</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>4809.6</v>
+        <v>4888.87</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>783.01</v>
+        <v>772.9299999999999</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1067.99</v>
+        <v>1060.45</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1817.66</v>
+        <v>1850.62</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1208.03</v>
+        <v>1229.93</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1256.77</v>
+        <v>1279.55</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1383.05</v>
+        <v>1408.12</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>4883.07</v>
+        <v>4959.56</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1984.26</v>
+        <v>2015.35</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2895.68</v>
+        <v>2941.04</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>912.45</v>
+        <v>912.4</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>4447.79</v>
+        <v>4447.56</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>13558.44</v>
+        <v>13557.74</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>825.9400000000001</v>
+        <v>822.25</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1211.51</v>
+        <v>1206.09</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1802.89</v>
+        <v>1794.83</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2073.2</v>
+        <v>2074.98</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>818.2</v>
+        <v>818.91</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>4252.14</v>
+        <v>4240.41</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>956.17</v>
+        <v>953.53</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>3157.43</v>
+        <v>3148.72</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>4531.69</v>
+        <v>4512.16</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1218.13</v>
+        <v>1212.88</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>5336.91</v>
+        <v>5313.91</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>2450.81</v>
+        <v>2415.35</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1352.49</v>
+        <v>1323.4</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1851.99</v>
+        <v>1812.14</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1731.93</v>
+        <v>1694.67</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1481.63</v>
+        <v>1447.16</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1193.55</v>
+        <v>1155.5</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>3351.51</v>
+        <v>3244.64</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1179.43</v>
+        <v>1141.82</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>779.75</v>
+        <v>758.88</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1113.45</v>
+        <v>1116.69</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>7811.17</v>
+        <v>7843.64</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1478.08</v>
+        <v>1484.22</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1900</v>
+        <v>1916.13</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>14740.84</v>
+        <v>14865.94</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2426.95</v>
+        <v>2456.82</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>4465.32</v>
+        <v>4520.27</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1165.61</v>
+        <v>1181.12</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>832.4299999999999</v>
+        <v>852.91</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>946.9299999999999</v>
+        <v>957.6900000000001</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2141.61</v>
+        <v>2155.31</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>9240.58</v>
+        <v>9269.66</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1060.56</v>
+        <v>1063.9</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>2175.4</v>
+        <v>2179.91</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>5865.27</v>
+        <v>5877.42</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1019.24</v>
+        <v>1014.86</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>874.41</v>
+        <v>869.17</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1502.94</v>
+        <v>1493.93</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>780.28</v>
+        <v>769.67</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1933.14</v>
+        <v>1954.76</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2219.95</v>
+        <v>2244.78</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>831.02</v>
+        <v>840.3099999999999</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1614.29</v>
+        <v>1626.52</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1503.83</v>
+        <v>1518.11</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>948.54</v>
+        <v>957.55</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1501.2</v>
+        <v>1486.23</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>985.66</v>
+        <v>981.34</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>1271.18</v>
+        <v>1257.35</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2418.21</v>
+        <v>2391.91</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1491.68</v>
+        <v>1475.45</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1458.26</v>
+        <v>1454.95</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>806.28</v>
+        <v>804.29</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>4460.46</v>
+        <v>4484.17</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>4098.02</v>
+        <v>4156.66</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1333.74</v>
+        <v>1352.82</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>8006.36</v>
+        <v>8100.28</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>962.1</v>
+        <v>978.37</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2309.04</v>
+        <v>2348.09</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1769.22</v>
+        <v>1785.82</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>793.04</v>
+        <v>787.02</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>793.6900000000001</v>
+        <v>780.28</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>1584.91</v>
+        <v>1558.13</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>793.83</v>
+        <v>780.42</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>1094.52</v>
+        <v>1076.03</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2185.22</v>
+        <v>2154.2</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>796.49</v>
+        <v>785.1799999999999</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>2073.28</v>
+        <v>2043.85</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1499.05</v>
+        <v>1478.45</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>830.62</v>
+        <v>842.99</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1441.43</v>
+        <v>1473.93</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1138.13</v>
+        <v>1163.79</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2120.72</v>
+        <v>2168.55</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1214.29</v>
+        <v>1241.68</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>800.14</v>
+        <v>805.67</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1633.4</v>
+        <v>1638.45</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1371.37</v>
+        <v>1375.61</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>3835.83</v>
+        <v>3847.69</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>4047.86</v>
+        <v>4060.38</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>5277.09</v>
+        <v>5206.8</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>801.87</v>
+        <v>791.1900000000001</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1847.57</v>
+        <v>1811.41</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>3539.66</v>
+        <v>3470.38</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1145.78</v>
+        <v>1123.35</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1285.35</v>
+        <v>1260.19</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>2033.6</v>
+        <v>1993.79</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>829.84</v>
+        <v>812.79</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>3295.51</v>
+        <v>3308.38</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>3622.53</v>
+        <v>3658.96</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>815.33</v>
+        <v>819.48</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>4581.2</v>
+        <v>4599.03</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1977.94</v>
+        <v>1982.16</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>3395.38</v>
+        <v>3403.17</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>7818.97</v>
+        <v>7871.31</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>1597.74</v>
+        <v>1608.92</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>1796.9</v>
+        <v>1809.47</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1342.15</v>
+        <v>1337.91</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>3355.37</v>
+        <v>3348.64</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>1267.59</v>
+        <v>1260.25</v>
       </c>
     </row>
     <row r="180">
@@ -11427,13 +11427,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>2832.06</v>
+        <v>2818.14</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>3335-864-CM26</t>
+          <t>5617-18-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>1301.45</v>
+        <v>885.54</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>5617-18-CM26</t>
+          <t>3335-864-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11519,12 +11519,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11534,12 +11534,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -11549,7 +11549,68 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>879.66</v>
+        <v>1310.16</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>707424-68-CM26</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="n">
+        <v>1452.22</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/los-rios.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M254"/>
+  <dimension ref="A1:M269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2527,7 +2527,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1497-197-CM25</t>
+          <t>1497-199-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SURTI VENTAS S.A.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.462.500-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2266.18</v>
+        <v>2188.23</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1497-199-CM25</t>
+          <t>1497-197-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SURTI VENTAS S.A.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.462.500-5</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2188.23</v>
+        <v>2266.18</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1035685-285-CM25</t>
+          <t>3789-556-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>AMINORTE S A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>99.533.780-0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1051.39</v>
+        <v>3089.61</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3789-556-CM25</t>
+          <t>1035685-285-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>AMINORTE S A</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>99.533.780-0</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3089.61</v>
+        <v>1051.39</v>
       </c>
     </row>
     <row r="39">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERPLAC LOS RIOS</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5699,7 +5699,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3335-15-CM26</t>
+          <t>3335-16-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.205.722-9</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1821.94</v>
+        <v>1309.24</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3335-16-CM26</t>
+          <t>3568-35-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5780,17 +5780,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>69.201.200-3</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1309.24</v>
+        <v>2306.19</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3568-35-CM26</t>
+          <t>3335-15-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5841,17 +5841,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.201.200-3</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2306.19</v>
+        <v>1821.94</v>
       </c>
     </row>
     <row r="90">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6370,7 +6370,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1057548-78-CM26</t>
+          <t>5955-83-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6390,17 +6390,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.607.503-9</t>
+          <t>69.201.100-7</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1034.9</v>
+        <v>1245.41</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1057548-79-CM26</t>
+          <t>5955-82-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6451,17 +6451,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.607.503-9</t>
+          <t>69.201.100-7</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1576.58</v>
+        <v>1776.48</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5955-82-CM26</t>
+          <t>1057548-78-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6512,17 +6512,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>69.201.100-7</t>
+          <t>61.607.503-9</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1776.48</v>
+        <v>1034.9</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5955-83-CM26</t>
+          <t>1057548-79-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6573,17 +6573,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>69.201.100-7</t>
+          <t>61.607.503-9</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1245.41</v>
+        <v>1576.58</v>
       </c>
     </row>
     <row r="102">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6736,7 +6736,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3850-11-CM26</t>
+          <t>2180-7-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Distribuidora Surmontt</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>76.287.477-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2125.07</v>
+        <v>825.9400000000001</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3850-12-CM26</t>
+          <t>1067355-73-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>61.980.670-0</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Distribuidora Surmontt</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>76.287.477-6</t>
+          <t>78.178.530-k</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1724.5</v>
+        <v>2226.98</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2180-7-CM26</t>
+          <t>3850-11-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>Distribuidora Surmontt</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.287.477-6</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>825.9400000000001</v>
+        <v>2125.07</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1067355-73-CM26</t>
+          <t>3850-12-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6939,17 +6939,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.980.670-0</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>Distribuidora Surmontt</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
+          <t>76.287.477-6</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2226.98</v>
+        <v>1724.5</v>
       </c>
     </row>
     <row r="108">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL XIV REGION DE LOS RIOS</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7102,7 +7102,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1432083-82-CM26</t>
+          <t>1267926-6-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>71.016.300-6</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>1254.01</v>
+        <v>947.09</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1432083-83-CM26</t>
+          <t>1723-92-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7183,17 +7183,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>5447.03</v>
+        <v>1348.9</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1340-50-CM26</t>
+          <t>1432083-83-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7244,17 +7244,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1243.05</v>
+        <v>5447.03</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1267926-6-CM26</t>
+          <t>1432083-82-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>71.016.300-6</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>947.09</v>
+        <v>1254.01</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1723-92-CM26</t>
+          <t>1340-50-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1348.9</v>
+        <v>1243.05</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2910-17-CM26</t>
+          <t>1067355-78-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>61.980.670-0</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>2364.15</v>
+        <v>1988.34</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1067355-78-CM26</t>
+          <t>2910-17-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.980.670-0</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>1988.34</v>
+        <v>2364.15</v>
       </c>
     </row>
     <row r="117">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I Municipalidad de Lago Ranco</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7712,7 +7712,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1057545-155-CM26</t>
+          <t>2910-26-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.607.500-4</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
+          <t>AMINORTE S A</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>78.067.906-9</t>
+          <t>99.533.780-0</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>3972.55</v>
+        <v>851.39</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2910-26-CM26</t>
+          <t>1057545-155-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>61.607.500-4</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>SERVICIO DE SALUD LOS RIOS</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>AMINORTE S A</t>
+          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>99.533.780-0</t>
+          <t>78.067.906-9</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>851.39</v>
+        <v>3972.55</v>
       </c>
     </row>
     <row r="122">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8322,7 +8322,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2180-16-CM26</t>
+          <t>3140-4515-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8342,17 +8342,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.201.100-7</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>1850.62</v>
+        <v>1279.55</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>3335-154-CM26</t>
+          <t>3140-4516-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8403,17 +8403,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>69.201.100-7</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1229.93</v>
+        <v>1408.12</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3140-4515-CM26</t>
+          <t>2180-16-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8464,17 +8464,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>69.201.100-7</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1279.55</v>
+        <v>1850.62</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3140-4516-CM26</t>
+          <t>3335-154-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8525,17 +8525,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>69.201.100-7</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1408.12</v>
+        <v>1229.93</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1426100-41-CM26</t>
+          <t>5740-76-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2941.04</v>
+        <v>2015.35</v>
       </c>
     </row>
     <row r="135">
@@ -8688,7 +8688,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>5740-76-CM26</t>
+          <t>1426100-41-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2015.35</v>
+        <v>2941.04</v>
       </c>
     </row>
     <row r="137">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9115,7 +9115,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>3850-77-CM26</t>
+          <t>1057545-262-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9135,17 +9135,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>61.607.500-4</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>SERVICIO DE SALUD LOS RIOS</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.067.906-9</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>2074.98</v>
+        <v>818.91</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1057545-262-CM26</t>
+          <t>3850-77-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9196,17 +9196,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.607.500-4</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>78.067.906-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>818.91</v>
+        <v>2074.98</v>
       </c>
     </row>
     <row r="145">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERPLAC LOS RIOS</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10853,7 +10853,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11555,7 +11555,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3335-514-CM26</t>
+          <t>3335-515-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -11610,13 +11610,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>957.55</v>
+        <v>1518.11</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>3335-515-CM26</t>
+          <t>3335-514-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11656,12 +11656,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1518.11</v>
+        <v>957.55</v>
       </c>
     </row>
     <row r="185">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL XIV REGION DE LOS RIOS</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12592,7 +12592,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1432083-1310-CM26</t>
+          <t>1723-315-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12612,17 +12612,17 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
@@ -12647,13 +12647,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>780.28</v>
+        <v>1076.03</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1305560-57-CM26</t>
+          <t>1432083-1330-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12673,7 +12673,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -12708,13 +12708,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>1558.13</v>
+        <v>780.42</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1432083-1330-CM26</t>
+          <t>1305560-57-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -12769,13 +12769,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>780.42</v>
+        <v>1558.13</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1723-315-CM26</t>
+          <t>1432083-1310-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12795,17 +12795,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12815,12 +12815,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -12830,13 +12830,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>1076.03</v>
+        <v>780.28</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>5740-204-CM26</t>
+          <t>3850-283-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12856,17 +12856,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12876,12 +12876,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -12891,13 +12891,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>785.1799999999999</v>
+        <v>2043.85</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>5740-205-CM26</t>
+          <t>5740-204-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -12937,12 +12937,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -12952,13 +12952,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>2154.2</v>
+        <v>785.1799999999999</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>3850-283-CM26</t>
+          <t>5740-205-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12978,17 +12978,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>2043.85</v>
+        <v>2154.2</v>
       </c>
     </row>
     <row r="207">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13141,7 +13141,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>983344-14-CM26</t>
+          <t>707424-47-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13166,12 +13166,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>65.144.279-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Ejército de Chile</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13181,12 +13181,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -13196,13 +13196,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1473.93</v>
+        <v>1241.68</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>299-101-CM26</t>
+          <t>2180-88-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13222,17 +13222,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13242,12 +13242,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
@@ -13257,13 +13257,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>1163.79</v>
+        <v>2168.55</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2180-88-CM26</t>
+          <t>299-101-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13283,17 +13283,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13303,12 +13303,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
@@ -13318,13 +13318,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>2168.55</v>
+        <v>1163.79</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>707424-47-CM26</t>
+          <t>983344-14-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13349,12 +13349,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.144.279-6</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1241.68</v>
+        <v>1473.93</v>
       </c>
     </row>
     <row r="213">
@@ -13690,7 +13690,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1057548-690-CM26</t>
+          <t>1035685-200-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13710,17 +13710,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>61.607.503-9</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13730,12 +13730,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
@@ -13745,13 +13745,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>5206.8</v>
+        <v>791.1900000000001</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1035685-200-CM26</t>
+          <t>1057548-690-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13771,17 +13771,17 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>61.607.503-9</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
@@ -13806,13 +13806,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>791.1900000000001</v>
+        <v>5206.8</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>5612-127-CM26</t>
+          <t>5538-155-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13837,12 +13837,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13852,12 +13852,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -13867,13 +13867,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>1993.79</v>
+        <v>1811.41</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>5538-157-CM26</t>
+          <t>5538-156-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13928,13 +13928,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>1123.35</v>
+        <v>3470.38</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>5538-158-CM26</t>
+          <t>5538-157-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13974,12 +13974,12 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -13989,13 +13989,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>1260.19</v>
+        <v>1123.35</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>5538-155-CM26</t>
+          <t>5538-158-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14050,13 +14050,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>1811.41</v>
+        <v>1260.19</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>5538-156-CM26</t>
+          <t>5612-127-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14081,12 +14081,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14096,12 +14096,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>3470.38</v>
+        <v>1993.79</v>
       </c>
     </row>
     <row r="225">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>I Municipalidad de Lago Ranco</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14869,7 +14869,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -14879,7 +14879,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -14930,7 +14930,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -15520,7 +15520,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1057547-12322-CM26</t>
+          <t>1189881-17-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15535,22 +15535,22 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15560,12 +15560,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>ECOFFICE COMPUTACION LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>76.293.503-1</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
@@ -15575,13 +15575,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>873.88</v>
+        <v>1262.16</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>5658-23-CM26</t>
+          <t>1057547-12322-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15596,7 +15596,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -15606,12 +15606,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15621,12 +15621,12 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>ECOFFICE COMPUTACION LIMITADA</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.293.503-1</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
@@ -15636,13 +15636,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>911.22</v>
+        <v>873.88</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1067355-390-CM26</t>
+          <t>5658-23-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15657,7 +15657,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -15667,12 +15667,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>61.980.670-0</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>1831.11</v>
+        <v>911.22</v>
       </c>
     </row>
     <row r="251">
@@ -15764,7 +15764,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1432083-2044-CM26</t>
+          <t>1067355-390-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -15779,7 +15779,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -15789,12 +15789,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.980.670-0</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15804,12 +15804,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
@@ -15819,13 +15819,13 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>1042.74</v>
+        <v>1831.11</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>3335-1060-CM26</t>
+          <t>1432083-2044-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -15840,22 +15840,22 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
@@ -15880,13 +15880,13 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>1585.27</v>
+        <v>1042.74</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>707424-68-CM26</t>
+          <t>3335-1060-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -15901,22 +15901,22 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -15941,7 +15941,922 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
+        <v>1585.27</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>707424-68-CM26</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M255" s="2" t="n">
         <v>1452.22</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>3545-223-CM26</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>65.273.020-5</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M256" s="2" t="n">
+        <v>2142.72</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>1057545-1007-CM26</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>61.607.500-4</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD LOS RIOS</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>78.067.906-9</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M257" s="2" t="n">
+        <v>1273.26</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>1057547-13482-CM26</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M258" s="2" t="n">
+        <v>10691.69</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>3141-201-CM26</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>69.201.100-7</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M259" s="2" t="n">
+        <v>1196.54</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>1432083-2134-CM26</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M260" s="2" t="n">
+        <v>973.37</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>3568-625-CM26</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>69.201.200-3</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M261" s="2" t="n">
+        <v>2146.38</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>5688-65-CM26</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>61.978.910-5</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>78.085.401-4</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M262" s="2" t="n">
+        <v>1936.25</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>5688-66-CM26</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>61.978.910-5</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M263" s="2" t="n">
+        <v>1083.08</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>1432083-2268-CM26</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M264" s="2" t="n">
+        <v>749.61</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>1432083-2269-CM26</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M265" s="2" t="n">
+        <v>1040.7</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>1057547-14049-CM26</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>ECOFFICE COMPUTACION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>76.293.503-1</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M266" s="2" t="n">
+        <v>1942.75</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>983344-32-CM26</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>65.144.279-6</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M267" s="2" t="n">
+        <v>761.39</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>1057547-14258-CM26</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M268" s="2" t="n">
+        <v>1614.25</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>1426100-172-CM26</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M269" s="2" t="n">
+        <v>2027.79</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/los-rios.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M373"/>
+  <dimension ref="A1:M391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1335,7 +1335,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1057548-99-CM25</t>
+          <t>1267926-3-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1360,12 +1360,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.607.503-9</t>
+          <t>71.016.300-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1375,32 +1375,28 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.041.579-0</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1308.85</v>
+        <v>1422.04</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1057548-98-CM25</t>
+          <t>1067355-68-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1425,12 +1421,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.607.503-9</t>
+          <t>61.980.670-0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1440,28 +1436,32 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.041.579-0</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1757.1</v>
+        <v>2082.57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1267926-3-CM25</t>
+          <t>952946-20-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>71.016.300-6</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1501,28 +1501,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.041.579-0</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1422.04</v>
+        <v>3263.06</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>952946-20-CM25</t>
+          <t>1057548-99-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1547,12 +1551,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.607.503-9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1562,17 +1566,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1581,13 +1585,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3263.06</v>
+        <v>1308.85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1067355-68-CM25</t>
+          <t>1057548-98-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1612,12 +1616,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.980.670-0</t>
+          <t>61.607.503-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1627,32 +1631,28 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.041.579-0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2082.57</v>
+        <v>1757.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1057547-6124-CM25</t>
+          <t>1057547-6125-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1692,17 +1692,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1711,13 +1711,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1251.13</v>
+        <v>1282.54</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1057547-6125-CM25</t>
+          <t>1057547-6124-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1757,17 +1757,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1282.54</v>
+        <v>1251.13</v>
       </c>
     </row>
     <row r="22">
@@ -2274,7 +2274,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1057549-89-CM25</t>
+          <t>1218393-95-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.607.504-7</t>
+          <t>53.335.808-K</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LANC</t>
+          <t>CONSULTORIO EXTERNO VALDIVIA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2314,12 +2314,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
+          <t>INVERSIONES CATALUÑA SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.041.579-0</t>
+          <t>76.961.219-k</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2329,13 +2329,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1261.66</v>
+        <v>1088.86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1057549-90-CM25</t>
+          <t>1057549-89-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2375,32 +2375,28 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.041.579-0</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>878.26</v>
+        <v>1261.66</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1218393-95-CM25</t>
+          <t>1057549-90-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2425,12 +2421,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>53.335.808-K</t>
+          <t>61.607.504-7</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>CONSULTORIO EXTERNO VALDIVIA</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LANC</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2440,28 +2436,32 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>INVERSIONES CATALUÑA SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.961.219-k</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1088.86</v>
+        <v>878.26</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>707424-9-CM25</t>
+          <t>707424-6-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2520,13 +2520,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2435.92</v>
+        <v>12448.91</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>707424-6-CM25</t>
+          <t>707424-9-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>12448.91</v>
+        <v>2435.92</v>
       </c>
     </row>
     <row r="35">
@@ -2835,7 +2835,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3335-150-CM25</t>
+          <t>1057553-1520-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.607.509-8</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2894,7 +2894,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>846.6900000000001</v>
+        <v>2081.82</v>
       </c>
     </row>
     <row r="40">
@@ -2961,7 +2961,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1057553-1520-CM25</t>
+          <t>3335-150-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.607.509-8</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3001,12 +3001,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2081.82</v>
+        <v>846.6900000000001</v>
       </c>
     </row>
     <row r="42">
@@ -3587,7 +3587,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3850-139-CM25</t>
+          <t>1067355-174-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3607,17 +3607,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>61.980.670-0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3642,13 +3642,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1153.51</v>
+        <v>2260.58</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1432083-268-CM25</t>
+          <t>3850-139-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3688,32 +3688,28 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.041.579-0</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>826.85</v>
+        <v>1153.51</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1067355-174-CM25</t>
+          <t>1432083-268-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3738,12 +3734,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.980.670-0</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3753,22 +3749,26 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.041.579-0</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2260.58</v>
+        <v>826.85</v>
       </c>
     </row>
     <row r="54">
@@ -3900,7 +3900,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5955-227-CM25</t>
+          <t>3545-81-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.201.100-7</t>
+          <t>65.273.020-5</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3940,32 +3940,28 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.041.579-0</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1454.69</v>
+        <v>4397.83</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3545-81-CM25</t>
+          <t>5955-227-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3985,17 +3981,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>65.273.020-5</t>
+          <t>69.201.100-7</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4005,22 +4001,26 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.041.579-0</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>4397.83</v>
+        <v>1454.69</v>
       </c>
     </row>
     <row r="58">
@@ -4152,7 +4152,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4777-1924-CM25</t>
+          <t>1057547-17213-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4172,17 +4172,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4192,32 +4192,28 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.041.579-0</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1601.7</v>
+        <v>5253.47</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1057547-17213-CM25</t>
+          <t>1057547-17217-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4272,13 +4268,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>5253.47</v>
+        <v>1476.22</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1057547-17217-CM25</t>
+          <t>4777-1924-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4298,17 +4294,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4318,22 +4314,26 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.041.579-0</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>77.610.393-4</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1476.22</v>
+        <v>1601.7</v>
       </c>
     </row>
     <row r="63">
@@ -4404,7 +4404,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5538-140-CM25</t>
+          <t>5538-141-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>INVERSIONES Y RENTAS AMINORTE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.432.149-9</t>
+          <t>76.041.579-0</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4459,13 +4459,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1168.73</v>
+        <v>3883.6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5538-141-CM25</t>
+          <t>5538-140-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
+          <t>INVERSIONES Y RENTAS AMINORTE LIMITADA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.041.579-0</t>
+          <t>76.432.149-9</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>3883.6</v>
+        <v>1168.73</v>
       </c>
     </row>
     <row r="66">
@@ -5270,7 +5270,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1218393-1818-CM25</t>
+          <t>3850-275-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5290,17 +5290,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>53.335.808-K</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>CONSULTORIO EXTERNO VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5325,13 +5325,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>820.96</v>
+        <v>4567.31</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3850-275-CM25</t>
+          <t>1218393-1818-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5351,17 +5351,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>53.335.808-K</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>CONSULTORIO EXTERNO VALDIVIA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>4567.31</v>
+        <v>820.96</v>
       </c>
     </row>
     <row r="80">
@@ -6148,7 +6148,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1057549-263-CM25</t>
+          <t>3986-204-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6168,17 +6168,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.607.504-7</t>
+          <t>69.200.200-8</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LANC</t>
+          <t>MUNICIPALIDAD DE CORRAL</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6188,28 +6188,32 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>76.041.579-0</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>924.89</v>
+        <v>1126.67</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3986-204-CM25</t>
+          <t>1057549-263-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6229,17 +6233,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.200.200-8</t>
+          <t>61.607.504-7</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CORRAL</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LANC</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6249,26 +6253,22 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.041.579-0</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>1126.67</v>
+        <v>924.89</v>
       </c>
     </row>
     <row r="94">
@@ -6339,7 +6339,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>952946-124-CM25</t>
+          <t>1057547-23330-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6398,13 +6398,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>796.48</v>
+        <v>1752.78</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3335-779-CM25</t>
+          <t>952946-124-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6424,17 +6424,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6463,13 +6463,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>807</v>
+        <v>796.48</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1057547-23330-CM25</t>
+          <t>3335-779-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6489,17 +6489,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1752.78</v>
+        <v>807</v>
       </c>
     </row>
     <row r="98">
@@ -6851,7 +6851,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1432083-801-CM25</t>
+          <t>5688-49-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6876,12 +6876,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.978.910-5</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6891,32 +6891,28 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.041.579-0</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1308.41</v>
+        <v>2836.04</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5688-49-CM25</t>
+          <t>1432083-801-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6941,12 +6937,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.978.910-5</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6956,22 +6952,26 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>76.041.579-0</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2836.04</v>
+        <v>1308.41</v>
       </c>
     </row>
     <row r="105">
@@ -7688,7 +7688,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2905-589-CM25</t>
+          <t>707424-66-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7747,7 +7747,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>1168.31</v>
+        <v>1040.88</v>
       </c>
     </row>
     <row r="117">
@@ -7818,7 +7818,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>707424-66-CM25</t>
+          <t>2905-589-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7877,13 +7877,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1040.88</v>
+        <v>1168.31</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>3335-1214-CM25</t>
+          <t>3335-1211-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7923,28 +7923,32 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>AMINORTE S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>99.533.780-0</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>768.72</v>
+        <v>1051.59</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3335-1211-CM25</t>
+          <t>3335-1214-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7984,32 +7988,28 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>AMINORTE S A</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>99.533.780-0</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1051.59</v>
+        <v>768.72</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1432083-971-CM25</t>
+          <t>1432083-970-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8068,13 +8068,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>725.9</v>
+        <v>2226.51</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1432083-970-CM25</t>
+          <t>1432083-971-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2226.51</v>
+        <v>725.9</v>
       </c>
     </row>
     <row r="123">
@@ -8269,7 +8269,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1432083-1040-CM25</t>
+          <t>1305560-137-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8328,13 +8328,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1646.55</v>
+        <v>2590.62</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1305560-137-CM25</t>
+          <t>1432083-1040-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8393,7 +8393,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2590.62</v>
+        <v>1646.55</v>
       </c>
     </row>
     <row r="127">
@@ -8919,7 +8919,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1218393-2005-CM25</t>
+          <t>1035685-271-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8944,12 +8944,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>53.335.808-K</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>CONSULTORIO EXTERNO VALDIVIA</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8959,17 +8959,17 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8978,13 +8978,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1385.7</v>
+        <v>1010.89</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1035685-271-CM25</t>
+          <t>1218393-2005-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>53.335.808-K</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>CONSULTORIO EXTERNO VALDIVIA</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9024,17 +9024,17 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -9043,7 +9043,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1010.89</v>
+        <v>1385.7</v>
       </c>
     </row>
     <row r="137">
@@ -10272,7 +10272,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1057553-1829-CM25</t>
+          <t>4777-2456-CM25</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10292,17 +10292,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.607.509-8</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10312,12 +10312,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -10331,13 +10331,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1294.17</v>
+        <v>1849.79</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>4777-2456-CM25</t>
+          <t>1057553-1829-CM25</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10357,17 +10357,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.607.509-8</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -10396,13 +10396,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1849.79</v>
+        <v>1294.17</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1432083-1593-CM25</t>
+          <t>1432083-1592-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10461,13 +10461,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1445.96</v>
+        <v>1480.47</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1432083-1592-CM25</t>
+          <t>1432083-1593-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10526,7 +10526,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>1480.47</v>
+        <v>1445.96</v>
       </c>
     </row>
     <row r="160">
@@ -13246,7 +13246,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1057548-78-CM26</t>
+          <t>1057548-79-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13286,17 +13286,17 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -13305,13 +13305,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>1034.9</v>
+        <v>1576.58</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1057548-79-CM26</t>
+          <t>5955-82-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13331,17 +13331,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>61.607.503-9</t>
+          <t>69.201.100-7</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13351,17 +13351,17 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -13370,13 +13370,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>1576.58</v>
+        <v>1776.48</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>5955-82-CM26</t>
+          <t>5955-83-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13416,12 +13416,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -13435,13 +13435,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>1776.48</v>
+        <v>1245.41</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>5955-83-CM26</t>
+          <t>1057548-78-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13461,17 +13461,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>69.201.100-7</t>
+          <t>61.607.503-9</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -13500,7 +13500,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1245.41</v>
+        <v>1034.9</v>
       </c>
     </row>
     <row r="206">
@@ -13636,7 +13636,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>3850-11-CM26</t>
+          <t>3850-12-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13691,13 +13691,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>2125.07</v>
+        <v>1724.5</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>3850-12-CM26</t>
+          <t>3850-11-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13752,13 +13752,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1724.5</v>
+        <v>2125.07</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2180-7-CM26</t>
+          <t>1067355-73-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13778,17 +13778,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.980.670-0</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13798,32 +13798,28 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.178.530-k</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>825.9400000000001</v>
+        <v>2226.98</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1067355-73-CM26</t>
+          <t>2180-7-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13843,17 +13839,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>61.980.670-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13863,22 +13859,26 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>2226.98</v>
+        <v>825.9400000000001</v>
       </c>
     </row>
     <row r="212">
@@ -14079,7 +14079,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1432083-83-CM26</t>
+          <t>1340-50-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -14099,17 +14099,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -14119,17 +14119,17 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>5447.03</v>
+        <v>1243.05</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1340-50-CM26</t>
+          <t>1267926-6-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14164,17 +14164,17 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>71.016.300-6</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -14184,17 +14184,17 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -14203,13 +14203,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1243.05</v>
+        <v>947.09</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1267926-6-CM26</t>
+          <t>1723-92-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14229,17 +14229,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>71.016.300-6</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -14249,17 +14249,17 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -14268,13 +14268,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>947.09</v>
+        <v>1348.9</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1723-92-CM26</t>
+          <t>1432083-83-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14294,17 +14294,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14314,17 +14314,17 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -14333,7 +14333,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>1348.9</v>
+        <v>5447.03</v>
       </c>
     </row>
     <row r="219">
@@ -14664,7 +14664,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1057545-155-CM26</t>
+          <t>2910-26-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>61.607.500-4</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14704,32 +14704,28 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
+          <t>AMINORTE S A</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>78.067.906-9</t>
-        </is>
-      </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>99.533.780-0</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>3972.55</v>
+        <v>851.39</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2910-26-CM26</t>
+          <t>1057545-155-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14754,12 +14750,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>61.607.500-4</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>SERVICIO DE SALUD LOS RIOS</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14769,28 +14765,32 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>AMINORTE S A</t>
+          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>99.533.780-0</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr"/>
+          <t>78.067.906-9</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>851.39</v>
+        <v>3972.55</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>509876-8-CM26</t>
+          <t>3850-40-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14810,17 +14810,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14830,17 +14830,17 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -14849,13 +14849,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>1989.84</v>
+        <v>806.48</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>3850-40-CM26</t>
+          <t>509876-8-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14875,17 +14875,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14895,17 +14895,17 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -14914,7 +14914,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>806.48</v>
+        <v>1989.84</v>
       </c>
     </row>
     <row r="228">
@@ -15440,7 +15440,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2180-16-CM26</t>
+          <t>3335-154-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15465,12 +15465,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -15499,13 +15499,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>1850.62</v>
+        <v>1229.93</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>3335-154-CM26</t>
+          <t>2180-16-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15530,12 +15530,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15545,12 +15545,12 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -15564,13 +15564,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>1229.93</v>
+        <v>1850.62</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1426100-41-CM26</t>
+          <t>5740-76-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15595,12 +15595,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15610,17 +15610,17 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -15629,7 +15629,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>2941.04</v>
+        <v>2015.35</v>
       </c>
     </row>
     <row r="239">
@@ -15700,7 +15700,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>5740-76-CM26</t>
+          <t>1426100-41-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15740,17 +15740,17 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -15759,13 +15759,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>2015.35</v>
+        <v>2941.04</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2910-34-CM26</t>
+          <t>1057545-236-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15790,12 +15790,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>61.607.500-4</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>SERVICIO DE SALUD LOS RIOS</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15805,28 +15805,32 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
-        </is>
-      </c>
-      <c r="K241" t="inlineStr"/>
+          <t>77.610.393-4</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>912.4</v>
+        <v>4447.56</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1057545-236-CM26</t>
+          <t>2910-34-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15851,12 +15855,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.607.500-4</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15866,26 +15870,22 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.205.722-9</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>4447.56</v>
+        <v>912.4</v>
       </c>
     </row>
     <row r="243">
@@ -15956,7 +15956,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1057549-115-CM26</t>
+          <t>1057549-116-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15996,17 +15996,17 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -16015,13 +16015,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>1206.09</v>
+        <v>1794.83</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1057549-116-CM26</t>
+          <t>1057549-115-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -16061,17 +16061,17 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -16080,7 +16080,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1794.83</v>
+        <v>1206.09</v>
       </c>
     </row>
     <row r="246">
@@ -16281,7 +16281,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>4777-219-CM26</t>
+          <t>3335-187-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16321,12 +16321,12 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -16340,7 +16340,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>3148.72</v>
+        <v>953.53</v>
       </c>
     </row>
     <row r="250">
@@ -16411,7 +16411,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>3335-187-CM26</t>
+          <t>4777-219-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16451,12 +16451,12 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -16470,13 +16470,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>953.53</v>
+        <v>3148.72</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>3335-226-CM26</t>
+          <t>3335-228-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16516,12 +16516,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -16535,7 +16535,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>5313.91</v>
+        <v>1212.88</v>
       </c>
     </row>
     <row r="253">
@@ -16606,7 +16606,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>3335-228-CM26</t>
+          <t>3335-226-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16646,12 +16646,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -16665,7 +16665,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>1212.88</v>
+        <v>5313.91</v>
       </c>
     </row>
     <row r="255">
@@ -16996,7 +16996,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2908-74-CM26</t>
+          <t>3335-257-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -17016,17 +17016,17 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -17036,17 +17036,17 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -17055,13 +17055,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1155.5</v>
+        <v>1141.82</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>5418-64-CM26</t>
+          <t>2908-74-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -17086,12 +17086,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -17101,17 +17101,17 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -17120,13 +17120,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>3244.64</v>
+        <v>1155.5</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>3335-257-CM26</t>
+          <t>5418-64-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -17146,17 +17146,17 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -17166,12 +17166,12 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -17185,7 +17185,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>1141.82</v>
+        <v>3244.64</v>
       </c>
     </row>
     <row r="263">
@@ -17447,7 +17447,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>707424-22-CM26</t>
+          <t>3850-144-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17467,17 +17467,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17506,13 +17506,13 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>14865.94</v>
+        <v>1916.13</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>3850-144-CM26</t>
+          <t>707424-22-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17532,17 +17532,17 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -17571,7 +17571,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>1916.13</v>
+        <v>14865.94</v>
       </c>
     </row>
     <row r="269">
@@ -18093,7 +18093,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>5612-56-CM26</t>
+          <t>1057547-6109-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -18113,17 +18113,17 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -18133,12 +18133,12 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2179.91</v>
+        <v>5877.42</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1057547-6109-CM26</t>
+          <t>5612-56-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -18178,17 +18178,17 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -18198,12 +18198,12 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -18217,7 +18217,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>5877.42</v>
+        <v>2179.91</v>
       </c>
     </row>
     <row r="279">
@@ -19003,7 +19003,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1432083-1122-CM26</t>
+          <t>1432083-1116-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -19023,7 +19023,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -19043,12 +19043,12 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
@@ -19062,7 +19062,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>1475.45</v>
+        <v>1257.35</v>
       </c>
     </row>
     <row r="292">
@@ -19133,7 +19133,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1432083-1116-CM26</t>
+          <t>1432083-1122-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -19153,7 +19153,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -19173,12 +19173,12 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -19192,7 +19192,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1257.35</v>
+        <v>1475.45</v>
       </c>
     </row>
     <row r="294">
@@ -19393,7 +19393,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1432083-1169-CM26</t>
+          <t>3789-293-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19413,17 +19413,17 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19452,13 +19452,13 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>4156.66</v>
+        <v>1352.82</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>3789-293-CM26</t>
+          <t>1432083-1169-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19478,17 +19478,17 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -19517,7 +19517,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>1352.82</v>
+        <v>4156.66</v>
       </c>
     </row>
     <row r="299">
@@ -19848,7 +19848,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>1432083-1310-CM26</t>
+          <t>1305560-57-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -19868,7 +19868,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -19907,13 +19907,13 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>780.28</v>
+        <v>1558.13</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1305560-57-CM26</t>
+          <t>1432083-1330-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -19933,7 +19933,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -19953,17 +19953,17 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -19972,13 +19972,13 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>1558.13</v>
+        <v>780.42</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>1432083-1330-CM26</t>
+          <t>1723-315-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -19998,17 +19998,17 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -20018,17 +20018,17 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -20037,13 +20037,13 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>780.42</v>
+        <v>1076.03</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1723-315-CM26</t>
+          <t>1432083-1310-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -20063,17 +20063,17 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -20083,12 +20083,12 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
@@ -20102,7 +20102,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>1076.03</v>
+        <v>780.28</v>
       </c>
     </row>
     <row r="308">
@@ -20433,7 +20433,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>707424-47-CM26</t>
+          <t>983344-14-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -20458,12 +20458,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.144.279-6</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -20473,17 +20473,17 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
@@ -20492,7 +20492,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>1241.68</v>
+        <v>1473.93</v>
       </c>
     </row>
     <row r="314">
@@ -20563,7 +20563,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>299-101-CM26</t>
+          <t>707424-47-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -20588,12 +20588,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -20603,17 +20603,17 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
@@ -20622,13 +20622,13 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>1163.79</v>
+        <v>1241.68</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>983344-14-CM26</t>
+          <t>299-101-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20653,12 +20653,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>65.144.279-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -20687,7 +20687,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>1473.93</v>
+        <v>1163.79</v>
       </c>
     </row>
     <row r="317">
@@ -20754,7 +20754,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>5538-146-CM26</t>
+          <t>5538-148-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -20794,12 +20794,12 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
@@ -20813,13 +20813,13 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>3847.69</v>
+        <v>4060.38</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>5538-148-CM26</t>
+          <t>5538-149-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -20859,12 +20859,12 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -20878,13 +20878,13 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>4060.38</v>
+        <v>1638.45</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>5538-149-CM26</t>
+          <t>5538-150-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -20924,12 +20924,12 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
@@ -20943,13 +20943,13 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>1638.45</v>
+        <v>1375.61</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>5538-150-CM26</t>
+          <t>5538-146-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -20989,12 +20989,12 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>1375.61</v>
+        <v>3847.69</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>1057548-690-CM26</t>
+          <t>1035685-200-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -21034,17 +21034,17 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>61.607.503-9</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -21054,17 +21054,17 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -21073,13 +21073,13 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>5206.8</v>
+        <v>791.1900000000001</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>1035685-200-CM26</t>
+          <t>1057548-690-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -21099,17 +21099,17 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>61.607.503-9</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -21119,17 +21119,17 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -21138,7 +21138,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>791.1900000000001</v>
+        <v>5206.8</v>
       </c>
     </row>
     <row r="324">
@@ -21209,7 +21209,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>5538-157-CM26</t>
+          <t>5538-158-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -21249,12 +21249,12 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -21268,13 +21268,13 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>1123.35</v>
+        <v>1260.19</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>5538-158-CM26</t>
+          <t>5538-157-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -21314,12 +21314,12 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -21333,7 +21333,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>1260.19</v>
+        <v>1123.35</v>
       </c>
     </row>
     <row r="327">
@@ -22834,7 +22834,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1057553-296-CM26</t>
+          <t>1057553-295-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -22854,7 +22854,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
@@ -22874,12 +22874,12 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
@@ -22893,13 +22893,13 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>816.25</v>
+        <v>850.75</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>1057553-295-CM26</t>
+          <t>1057553-296-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -22919,7 +22919,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -22939,12 +22939,12 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
@@ -22958,7 +22958,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>850.75</v>
+        <v>816.25</v>
       </c>
     </row>
     <row r="352">
@@ -23545,7 +23545,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1057547-13482-CM26</t>
+          <t>1057545-1007-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23570,12 +23570,12 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.607.500-4</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>SERVICIO DE SALUD LOS RIOS</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -23585,12 +23585,12 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>78.067.906-9</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
@@ -23604,13 +23604,13 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>10691.69</v>
+        <v>1273.26</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>1057545-1007-CM26</t>
+          <t>1057547-13482-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -23635,12 +23635,12 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>61.607.500-4</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LOS RIOS</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -23650,12 +23650,12 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>78.067.906-9</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
@@ -23669,7 +23669,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>1273.26</v>
+        <v>10691.69</v>
       </c>
     </row>
     <row r="363">
@@ -23870,7 +23870,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>5688-65-CM26</t>
+          <t>5688-66-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -23890,7 +23890,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -23910,17 +23910,17 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -23929,13 +23929,13 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>1936.25</v>
+        <v>1083.08</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>5688-66-CM26</t>
+          <t>1432083-2268-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -23955,17 +23955,17 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>61.978.910-5</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -23994,13 +23994,13 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>1083.08</v>
+        <v>749.61</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>1432083-2268-CM26</t>
+          <t>1432083-2269-CM26</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -24020,7 +24020,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
@@ -24059,13 +24059,13 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>749.61</v>
+        <v>1040.7</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>1432083-2269-CM26</t>
+          <t>5688-65-CM26</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -24085,17 +24085,17 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.978.910-5</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -24105,17 +24105,17 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
@@ -24124,7 +24124,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>1040.7</v>
+        <v>1936.25</v>
       </c>
     </row>
     <row r="370">
@@ -24321,66 +24321,1236 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
+          <t>1057548-1003-CM26</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>61.607.503-9</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M373" s="2" t="n">
+        <v>3298.23</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
           <t>1426100-172-CM26</t>
         </is>
       </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>2239-16-LR24</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr">
+      <c r="D374" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="E373" t="inlineStr">
+      <c r="E374" t="inlineStr">
         <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F373" t="inlineStr">
+      <c r="F374" t="inlineStr">
         <is>
           <t>62.000.970-9</t>
         </is>
       </c>
-      <c r="G373" t="inlineStr">
+      <c r="G374" t="inlineStr">
         <is>
           <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
-      <c r="H373" t="inlineStr">
-        <is>
-          <t>Los Ríos</t>
-        </is>
-      </c>
-      <c r="I373" t="inlineStr">
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
         </is>
       </c>
-      <c r="J373" t="inlineStr">
+      <c r="J374" t="inlineStr">
         <is>
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr">
+      <c r="K374" t="inlineStr">
         <is>
           <t>Antofagasta</t>
         </is>
       </c>
-      <c r="L373" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M373" s="2" t="n">
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M374" s="2" t="n">
         <v>2027.79</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>5538-270-CM26</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M375" s="2" t="n">
+        <v>857.9</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>5538-271-CM26</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M376" s="2" t="n">
+        <v>980.46</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>5538-272-CM26</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>77.610.393-4</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M377" s="2" t="n">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>5538-273-CM26</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>77.610.393-4</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M378" s="2" t="n">
+        <v>986.55</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>5751-261-CM26</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>61.818.002-6</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M379" s="2" t="n">
+        <v>1765.99</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2910-170-CM26</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>69.200.700-k</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>77.610.393-4</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M380" s="2" t="n">
+        <v>2552.43</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>1057553-375-CM26</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>61.607.509-8</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M381" s="2" t="n">
+        <v>881.0700000000001</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>5418-244-CM26</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>61.978.900-8</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M382" s="2" t="n">
+        <v>2086.04</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2180-192-CM26</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M383" s="2" t="n">
+        <v>1374.43</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>1723-629-CM26</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>69.200.600-3</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M384" s="2" t="n">
+        <v>744.12</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>1218393-468-CM26</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>53.335.808-K</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>CONSULTORIO EXTERNO VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M385" s="2" t="n">
+        <v>1221.08</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2180-201-CM26</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M386" s="2" t="n">
+        <v>799.97</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>5688-73-CM26</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>61.978.910-5</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>77.610.393-4</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M387" s="2" t="n">
+        <v>1896.15</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>1057547-15416-CM26</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M388" s="2" t="n">
+        <v>822.6</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>5740-392-CM26</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>61.979.060-k</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M389" s="2" t="n">
+        <v>956.51</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>5740-393-CM26</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>61.979.060-k</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M390" s="2" t="n">
+        <v>929.6900000000001</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>1057547-15501-CM26</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M391" s="2" t="n">
+        <v>6642.45</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/los-rios.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M394"/>
+  <dimension ref="A1:M395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14461,7 +14461,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1267926-6-CM26</t>
+          <t>1723-92-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14481,17 +14481,17 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>71.016.300-6</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14501,17 +14501,17 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -14520,13 +14520,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>947.09</v>
+        <v>1348.9</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1723-92-CM26</t>
+          <t>1267926-6-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14546,17 +14546,17 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>71.016.300-6</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14566,17 +14566,17 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -14585,13 +14585,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>1348.9</v>
+        <v>947.09</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2910-17-CM26</t>
+          <t>1067355-78-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14616,12 +14616,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>61.980.670-0</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14631,17 +14631,17 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -14650,13 +14650,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>2364.15</v>
+        <v>1988.34</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1067355-78-CM26</t>
+          <t>2910-17-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14681,12 +14681,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>61.980.670-0</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14696,17 +14696,17 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -14715,7 +14715,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1988.34</v>
+        <v>2364.15</v>
       </c>
     </row>
     <row r="225">
@@ -15627,7 +15627,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>3140-4515-CM26</t>
+          <t>3335-154-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15647,17 +15647,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>69.201.100-7</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15686,13 +15686,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>1279.55</v>
+        <v>1229.93</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>3335-154-CM26</t>
+          <t>3140-4515-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15712,17 +15712,17 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>69.201.100-7</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15751,7 +15751,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>1229.93</v>
+        <v>1279.55</v>
       </c>
     </row>
     <row r="241">
@@ -15822,7 +15822,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1057547-3829-CM26</t>
+          <t>5740-76-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15847,12 +15847,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15862,12 +15862,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -15881,13 +15881,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>4959.56</v>
+        <v>2015.35</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1426100-41-CM26</t>
+          <t>1057547-3829-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15912,12 +15912,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15927,17 +15927,17 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -15946,13 +15946,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>2941.04</v>
+        <v>4959.56</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>5740-76-CM26</t>
+          <t>1426100-41-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15977,12 +15977,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15992,17 +15992,17 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -16011,7 +16011,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>2015.35</v>
+        <v>2941.04</v>
       </c>
     </row>
     <row r="245">
@@ -16533,7 +16533,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>3335-187-CM26</t>
+          <t>1057548-230-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16553,17 +16553,17 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.607.503-9</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16573,17 +16573,17 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -16592,13 +16592,13 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>953.53</v>
+        <v>4240.41</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1057548-230-CM26</t>
+          <t>4777-219-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16618,17 +16618,17 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>61.607.503-9</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16638,17 +16638,17 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -16657,13 +16657,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>4240.41</v>
+        <v>3148.72</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>4777-219-CM26</t>
+          <t>3335-187-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16703,12 +16703,12 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -16722,13 +16722,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>3148.72</v>
+        <v>953.53</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>3335-226-CM26</t>
+          <t>3335-228-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -16787,13 +16787,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>5313.91</v>
+        <v>1212.88</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>3335-228-CM26</t>
+          <t>3335-226-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16833,12 +16833,12 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -16852,7 +16852,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>1212.88</v>
+        <v>5313.91</v>
       </c>
     </row>
     <row r="258">
@@ -16988,7 +16988,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1432083-529-CM26</t>
+          <t>3335-236-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -17008,17 +17008,17 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -17028,12 +17028,12 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -17047,13 +17047,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1323.4</v>
+        <v>1812.14</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>3335-242-CM26</t>
+          <t>1432083-529-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -17073,17 +17073,17 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -17112,13 +17112,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>1694.67</v>
+        <v>1323.4</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>3335-236-CM26</t>
+          <t>3335-242-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -17177,7 +17177,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>1812.14</v>
+        <v>1694.67</v>
       </c>
     </row>
     <row r="263">
@@ -17248,7 +17248,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>5418-64-CM26</t>
+          <t>2908-74-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -17273,12 +17273,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -17288,17 +17288,17 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -17307,13 +17307,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>3244.64</v>
+        <v>1155.5</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>3335-257-CM26</t>
+          <t>5418-64-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17333,17 +17333,17 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -17353,12 +17353,12 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -17372,13 +17372,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>1141.82</v>
+        <v>3244.64</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2908-74-CM26</t>
+          <t>3335-257-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17398,17 +17398,17 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -17418,17 +17418,17 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -17437,7 +17437,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>1155.5</v>
+        <v>1141.82</v>
       </c>
     </row>
     <row r="267">
@@ -17569,7 +17569,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>3335-315-CM26</t>
+          <t>3335-314-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17609,12 +17609,12 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -17628,13 +17628,13 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>1484.22</v>
+        <v>7843.64</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>3335-314-CM26</t>
+          <t>3335-315-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17674,12 +17674,12 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -17693,7 +17693,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>7843.64</v>
+        <v>1484.22</v>
       </c>
     </row>
     <row r="271">
@@ -17829,7 +17829,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1267885-360-CM26</t>
+          <t>1267885-359-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17888,13 +17888,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>4520.27</v>
+        <v>2456.82</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1267885-359-CM26</t>
+          <t>1267885-360-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17953,7 +17953,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>2456.82</v>
+        <v>4520.27</v>
       </c>
     </row>
     <row r="275">
@@ -18215,7 +18215,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>952946-73-CM26</t>
+          <t>1057550-126-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -18240,12 +18240,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.607.505-5</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -18274,13 +18274,13 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>1063.9</v>
+        <v>9269.66</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1057550-126-CM26</t>
+          <t>952946-73-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18305,12 +18305,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>61.607.505-5</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE C</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -18339,13 +18339,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>9269.66</v>
+        <v>1063.9</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>5612-56-CM26</t>
+          <t>1057547-6109-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18365,17 +18365,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -18385,12 +18385,12 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -18404,13 +18404,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>2179.91</v>
+        <v>5877.42</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1057547-6109-CM26</t>
+          <t>5612-56-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18430,17 +18430,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18450,12 +18450,12 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -18469,7 +18469,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>5877.42</v>
+        <v>2179.91</v>
       </c>
     </row>
     <row r="283">
@@ -18540,7 +18540,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1497-65-CM26</t>
+          <t>1497-63-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18580,17 +18580,17 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -18599,13 +18599,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>1493.93</v>
+        <v>869.17</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1497-63-CM26</t>
+          <t>1497-65-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18645,17 +18645,17 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -18664,7 +18664,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>869.17</v>
+        <v>1493.93</v>
       </c>
     </row>
     <row r="286">
@@ -18735,7 +18735,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>3986-163-CM26</t>
+          <t>3335-460-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -18760,12 +18760,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>69.200.200-8</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CORRAL</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -18775,17 +18775,17 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -18794,7 +18794,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>840.3099999999999</v>
+        <v>1954.76</v>
       </c>
     </row>
     <row r="288">
@@ -18865,7 +18865,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>3335-460-CM26</t>
+          <t>3986-163-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18890,12 +18890,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>69.200.200-8</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>MUNICIPALIDAD DE CORRAL</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18905,17 +18905,17 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -18924,7 +18924,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>1954.76</v>
+        <v>840.3099999999999</v>
       </c>
     </row>
     <row r="290">
@@ -19255,7 +19255,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>5688-40-CM26</t>
+          <t>1432083-1116-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19280,12 +19280,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>61.978.910-5</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -19295,17 +19295,17 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -19314,13 +19314,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>2391.91</v>
+        <v>1257.35</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1432083-1116-CM26</t>
+          <t>5688-40-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.978.910-5</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -19360,17 +19360,17 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -19379,7 +19379,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>1257.35</v>
+        <v>2391.91</v>
       </c>
     </row>
     <row r="297">
@@ -19645,7 +19645,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>3789-293-CM26</t>
+          <t>1432083-1169-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19665,17 +19665,17 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -19704,13 +19704,13 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>1352.82</v>
+        <v>4156.66</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>1432083-1169-CM26</t>
+          <t>3789-293-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -19730,17 +19730,17 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -19769,7 +19769,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>4156.66</v>
+        <v>1352.82</v>
       </c>
     </row>
     <row r="303">
@@ -20100,7 +20100,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>1432083-1330-CM26</t>
+          <t>1723-315-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -20120,17 +20120,17 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -20140,17 +20140,17 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -20159,13 +20159,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>780.42</v>
+        <v>1076.03</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1723-315-CM26</t>
+          <t>1432083-1330-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -20185,17 +20185,17 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -20205,17 +20205,17 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
@@ -20224,7 +20224,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>1076.03</v>
+        <v>780.42</v>
       </c>
     </row>
     <row r="310">
@@ -21071,7 +21071,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>5538-150-CM26</t>
+          <t>5538-148-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -21130,7 +21130,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>1375.61</v>
+        <v>4060.38</v>
       </c>
     </row>
     <row r="324">
@@ -21201,7 +21201,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>5538-148-CM26</t>
+          <t>5538-150-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -21260,13 +21260,13 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>4060.38</v>
+        <v>1375.61</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>1035685-200-CM26</t>
+          <t>1057548-690-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -21286,17 +21286,17 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>61.607.503-9</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -21306,17 +21306,17 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -21325,13 +21325,13 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>791.1900000000001</v>
+        <v>5206.8</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>1057548-690-CM26</t>
+          <t>1035685-200-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -21351,17 +21351,17 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>61.607.503-9</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -21371,17 +21371,17 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -21390,13 +21390,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>5206.8</v>
+        <v>791.1900000000001</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>5612-127-CM26</t>
+          <t>5538-157-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21421,12 +21421,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -21436,17 +21436,17 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -21455,13 +21455,13 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>1993.79</v>
+        <v>1123.35</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>5538-157-CM26</t>
+          <t>5538-155-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21501,12 +21501,12 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
@@ -21520,13 +21520,13 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>1123.35</v>
+        <v>1811.41</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>5538-156-CM26</t>
+          <t>5538-158-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21566,12 +21566,12 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
@@ -21585,13 +21585,13 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>3470.38</v>
+        <v>1260.19</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>5538-155-CM26</t>
+          <t>5612-127-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21616,12 +21616,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -21631,17 +21631,17 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -21650,13 +21650,13 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>1811.41</v>
+        <v>1993.79</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>5538-158-CM26</t>
+          <t>5538-156-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -21715,7 +21715,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>1260.19</v>
+        <v>3470.38</v>
       </c>
     </row>
     <row r="333">
@@ -22241,7 +22241,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1057547-10458-CM26</t>
+          <t>926853-45-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -22266,12 +22266,12 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -22281,12 +22281,12 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
@@ -22300,13 +22300,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>1809.47</v>
+        <v>1608.92</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>926853-45-CM26</t>
+          <t>1057547-10458-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22331,12 +22331,12 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -22346,12 +22346,12 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -22365,7 +22365,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>1608.92</v>
+        <v>1809.47</v>
       </c>
     </row>
     <row r="343">
@@ -22761,7 +22761,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>1057547-11619-CM26</t>
+          <t>1079694-241-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -22786,12 +22786,12 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -22801,17 +22801,17 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
@@ -22820,13 +22820,13 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>8366.48</v>
+        <v>12964.88</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1079694-241-CM26</t>
+          <t>1057547-11619-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -22851,12 +22851,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -22866,17 +22866,17 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
@@ -22885,13 +22885,13 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>12964.88</v>
+        <v>8366.48</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>1057549-384-CM26</t>
+          <t>1432083-1874-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -22916,12 +22916,12 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>61.607.504-7</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LANC</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -22931,12 +22931,12 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
@@ -22950,13 +22950,13 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>1029.59</v>
+        <v>998.15</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>1432083-1874-CM26</t>
+          <t>1057549-384-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -22981,12 +22981,12 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.607.504-7</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LANC</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -22996,12 +22996,12 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
@@ -23015,7 +23015,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>998.15</v>
+        <v>1029.59</v>
       </c>
     </row>
     <row r="353">
@@ -25048,7 +25048,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -25678,65 +25678,130 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
+          <t>3335-1478-CM26</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M394" s="2" t="n">
+        <v>1887.46</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
           <t>1057547-15501-CM26</t>
         </is>
       </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>2239-16-LR24</t>
-        </is>
-      </c>
-      <c r="C394" t="inlineStr">
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr">
+      <c r="D395" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E394" t="inlineStr">
+      <c r="E395" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F394" t="inlineStr">
+      <c r="F395" t="inlineStr">
         <is>
           <t>61.607.502-0</t>
         </is>
       </c>
-      <c r="G394" t="inlineStr">
+      <c r="G395" t="inlineStr">
         <is>
           <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
-      <c r="H394" t="inlineStr">
-        <is>
-          <t>Los Ríos</t>
-        </is>
-      </c>
-      <c r="I394" t="inlineStr">
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
         <is>
           <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
-      <c r="J394" t="inlineStr">
+      <c r="J395" t="inlineStr">
         <is>
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr">
+      <c r="K395" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L394" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M394" s="2" t="n">
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M395" s="2" t="n">
         <v>6642.45</v>
       </c>
     </row>
